--- a/output/pdf_financials_xlsx/MRU.xlsx
+++ b/output/pdf_financials_xlsx/MRU.xlsx
@@ -32608,7 +32608,11 @@
           <t>Additions to intangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -33642,7 +33646,11 @@
           <t>Additions to intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -35748,7 +35756,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E296" s="5" t="n">
         <v>-36.8</v>
       </c>
@@ -38640,7 +38652,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
